--- a/lead-tracker.xlsx
+++ b/lead-tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="120">
   <si>
     <t xml:space="preserve">Business Name</t>
   </si>
@@ -276,6 +276,63 @@
   </si>
   <si>
     <t xml:space="preserve">SAMPLE - DELETE ME. Case-study pricing (first 5 clients).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charleston Weddings by Allison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://google.com/maps/place/Charleston+Weddings+by+Allison/@32.9558666,-80.0550008,17z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 843-901-2111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charleston, SC (29406)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wedding service, 4.4 stars (5 reviews). No website on Maps. Need to find IG handle + confirm active.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabulous Fete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://google.com/maps/place/Fabulous+Fete/@32.7766115,-79.928047,17z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 843-609-7669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charleston, SC (29401)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wedding planner, 5.0 stars (33 reviews). CAUTION: Maps shows "may be closed" - verify still active on IG before building demo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amara Photography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://google.com/maps/place/Amara+Photography/@32.7875847,-79.9290819,17z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 843-608-9044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wedding photographer, 5.0 stars (6 reviews). No website on Maps, listing shows Open now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolutely Charleston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://google.com/maps/place/Absolutely+Charleston/@33.0042676,-80.1756363,17z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 843-747-4448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summerville, SC (29485)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event management company, 4.4 stars (20 reviews). No website on Maps, likely home-based.</t>
   </si>
   <si>
     <t xml:space="preserve">Legend / Instructions</t>
@@ -517,96 +574,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -916,1066 +977,1138 @@
   <dimension ref="A1:M58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="4" t="n">
         <v>46288</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="4" t="n">
         <v>46288</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9" t="s">
+      <c r="B12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="s">
+      <c r="E12" s="6" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9" t="s">
+      <c r="F12" s="6" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="9" t="s">
+      <c r="G12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="6" t="s">
         <v>89</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>46288</v>
+      </c>
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>46288</v>
+      </c>
+      <c r="M13" s="8"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>46288</v>
+      </c>
+      <c r="M14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>46288</v>
+      </c>
+      <c r="M15" s="8"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="10" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2039,189 +2172,189 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="12" t="n">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="13" t="n">
         <f aca="false">COUNTA(Leads!A2:A51)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A7)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A8)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A9)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A10)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A12)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A13)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A14)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="20" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A15)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="21" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A16)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="12" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="13" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,"DM Sent")+COUNTIF(Leads!H2:H51,"Replied")+COUNTIF(Leads!H2:H51,"WhatsApp")+COUNTIF(Leads!H2:H51,"Demo Sent")+COUNTIF(Leads!H2:H51,"Negotiating")+COUNTIF(Leads!H2:H51,"Deposit Paid")+COUNTIF(Leads!H2:H51,"Won")+COUNTIF(Leads!H2:H51,"Lost/Ghosted")</f>
         <v>8</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="12" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="13" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,"Won")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="21" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="22" t="n">
         <f aca="false">IFERROR(B20/B18,0)</f>
         <v>0.125</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="22" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="23" t="n">
         <f aca="false">SUM(Leads!J2:J51)</f>
         <v>1100</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B24" s="22" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="23" t="n">
         <f aca="false">SUMIF(Leads!H2:H51,"Won",Leads!I2:I51)+SUMIF(Leads!H2:H51,"Deposit Paid",Leads!I2:I51)</f>
         <v>2200</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B25" s="22" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="23" t="n">
         <f aca="false">IFERROR(SUMIF(Leads!H2:H51,"Won",Leads!I2:I51)/B20,0)</f>
         <v>1200</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/lead-tracker.xlsx
+++ b/lead-tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="130">
   <si>
     <t xml:space="preserve">Business Name</t>
   </si>
@@ -333,6 +333,36 @@
   </si>
   <si>
     <t xml:space="preserve">Event management company, 4.4 stars (20 reviews). No website on Maps, likely home-based.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loviebeks Photography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@loviebeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charleston, SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG: Charleston Wedding Photographer, 5114 followers, 1301 posts (very active). Bio link is a Dubsado CRM intake form, not a real site. Confirm actual business/brand name on first contact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nell's Florals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@nellsflorals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG: Charleston Wedding Florist, owner Jenn Sexton, 411 followers. No bio link at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charleston Bride Tribe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@charlestonbridetribe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG: #1 Charleston Bachelorette Photographer, 3252 followers, 175 posts (very active). Bio link is only a Linktree, no real website.</t>
   </si>
   <si>
     <t xml:space="preserve">Legend / Instructions</t>
@@ -1547,48 +1577,96 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>105</v>
+      </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="F16" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="8"/>
+      <c r="K16" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>46288</v>
+      </c>
       <c r="M16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="A17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="F17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="8"/>
+      <c r="K17" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>46288</v>
+      </c>
       <c r="M17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="A18" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="F18" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="8"/>
+      <c r="K18" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>46288</v>
+      </c>
       <c r="M18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2088,27 +2166,27 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2179,30 +2257,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B4" s="13" t="n">
         <f aca="false">COUNTA(Leads!A2:A51)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2220,7 +2298,7 @@
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A8)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2297,7 +2375,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B18" s="13" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,"DM Sent")+COUNTIF(Leads!H2:H51,"Replied")+COUNTIF(Leads!H2:H51,"WhatsApp")+COUNTIF(Leads!H2:H51,"Demo Sent")+COUNTIF(Leads!H2:H51,"Negotiating")+COUNTIF(Leads!H2:H51,"Deposit Paid")+COUNTIF(Leads!H2:H51,"Won")+COUNTIF(Leads!H2:H51,"Lost/Ghosted")</f>
@@ -2306,7 +2384,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B20" s="13" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,"Won")</f>
@@ -2315,7 +2393,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">IFERROR(B20/B18,0)</f>
@@ -2324,7 +2402,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">SUM(Leads!J2:J51)</f>
@@ -2333,7 +2411,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B24" s="23" t="n">
         <f aca="false">SUMIF(Leads!H2:H51,"Won",Leads!I2:I51)+SUMIF(Leads!H2:H51,"Deposit Paid",Leads!I2:I51)</f>
@@ -2342,7 +2420,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">IFERROR(SUMIF(Leads!H2:H51,"Won",Leads!I2:I51)/B20,0)</f>
@@ -2351,7 +2429,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>

--- a/lead-tracker.xlsx
+++ b/lead-tracker.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="134">
   <si>
     <t xml:space="preserve">Business Name</t>
   </si>
@@ -363,6 +363,18 @@
   </si>
   <si>
     <t xml:space="preserve">IG: #1 Charleston Bachelorette Photographer, 3252 followers, 175 posts (very active). Bio link is only a Linktree, no real website.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachel Craig Photography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://google.com/maps/place/Rachel+Craig+Photography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1 843-743-8567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wedding photographer, 5.0 stars (16 reviews), listing shows Open. No website (Maps flags it as missing info). Search IG for handle before outreach.</t>
   </si>
   <si>
     <t xml:space="preserve">Legend / Instructions</t>
@@ -1670,18 +1682,36 @@
       <c r="M18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="D19" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="8"/>
+      <c r="K19" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>46288</v>
+      </c>
       <c r="M19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2166,27 +2196,27 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2257,30 +2287,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B4" s="13" t="n">
         <f aca="false">COUNTA(Leads!A2:A51)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2298,7 +2328,7 @@
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,A8)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2375,7 +2405,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B18" s="13" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,"DM Sent")+COUNTIF(Leads!H2:H51,"Replied")+COUNTIF(Leads!H2:H51,"WhatsApp")+COUNTIF(Leads!H2:H51,"Demo Sent")+COUNTIF(Leads!H2:H51,"Negotiating")+COUNTIF(Leads!H2:H51,"Deposit Paid")+COUNTIF(Leads!H2:H51,"Won")+COUNTIF(Leads!H2:H51,"Lost/Ghosted")</f>
@@ -2384,7 +2414,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B20" s="13" t="n">
         <f aca="false">COUNTIF(Leads!H2:H51,"Won")</f>
@@ -2393,7 +2423,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">IFERROR(B20/B18,0)</f>
@@ -2402,7 +2432,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">SUM(Leads!J2:J51)</f>
@@ -2411,7 +2441,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B24" s="23" t="n">
         <f aca="false">SUMIF(Leads!H2:H51,"Won",Leads!I2:I51)+SUMIF(Leads!H2:H51,"Deposit Paid",Leads!I2:I51)</f>
@@ -2420,7 +2450,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B25" s="23" t="n">
         <f aca="false">IFERROR(SUMIF(Leads!H2:H51,"Won",Leads!I2:I51)/B20,0)</f>
@@ -2429,7 +2459,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
